--- a/artfynd/A 48349-2022 artfynd.xlsx
+++ b/artfynd/A 48349-2022 artfynd.xlsx
@@ -8024,7 +8024,7 @@
         <v>113315103</v>
       </c>
       <c r="B62" t="n">
-        <v>97298</v>
+        <v>97314</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>

--- a/artfynd/A 48349-2022 artfynd.xlsx
+++ b/artfynd/A 48349-2022 artfynd.xlsx
@@ -8024,7 +8024,7 @@
         <v>113315103</v>
       </c>
       <c r="B62" t="n">
-        <v>97314</v>
+        <v>97326</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>

--- a/artfynd/A 48349-2022 artfynd.xlsx
+++ b/artfynd/A 48349-2022 artfynd.xlsx
@@ -8024,7 +8024,7 @@
         <v>113315103</v>
       </c>
       <c r="B62" t="n">
-        <v>97326</v>
+        <v>97348</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>

--- a/artfynd/A 48349-2022 artfynd.xlsx
+++ b/artfynd/A 48349-2022 artfynd.xlsx
@@ -8024,7 +8024,7 @@
         <v>113315103</v>
       </c>
       <c r="B62" t="n">
-        <v>97348</v>
+        <v>97352</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>

--- a/artfynd/A 48349-2022 artfynd.xlsx
+++ b/artfynd/A 48349-2022 artfynd.xlsx
@@ -8024,7 +8024,7 @@
         <v>113315103</v>
       </c>
       <c r="B62" t="n">
-        <v>97352</v>
+        <v>97358</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>

--- a/artfynd/A 48349-2022 artfynd.xlsx
+++ b/artfynd/A 48349-2022 artfynd.xlsx
@@ -8024,7 +8024,7 @@
         <v>113315103</v>
       </c>
       <c r="B62" t="n">
-        <v>97358</v>
+        <v>97365</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>

--- a/artfynd/A 48349-2022 artfynd.xlsx
+++ b/artfynd/A 48349-2022 artfynd.xlsx
@@ -8024,7 +8024,7 @@
         <v>113315103</v>
       </c>
       <c r="B62" t="n">
-        <v>97365</v>
+        <v>97370</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>

--- a/artfynd/A 48349-2022 artfynd.xlsx
+++ b/artfynd/A 48349-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
